--- a/data/conf_ta_output/conf_ta_N.xlsx
+++ b/data/conf_ta_output/conf_ta_N.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -419,7 +419,7 @@
         <v>0.01</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D2">
         <v>1000</v>
@@ -440,10 +440,10 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>0.99</v>
+        <v>0.988</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0.5</v>
+        <v>0.498</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -510,10 +510,10 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -545,10 +545,10 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>0.07000000000000001</v>
+        <v>0.036</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -615,10 +615,10 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>0.04</v>
+        <v>0.054</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -650,10 +650,10 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -685,10 +685,10 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -720,10 +720,220 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>500</v>
+      </c>
+      <c r="B11">
+        <v>0.01</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <v>1000</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>0.05</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0.046</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>600</v>
+      </c>
+      <c r="B12">
+        <v>0.01</v>
+      </c>
+      <c r="C12">
+        <v>0.1</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>0.05</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0.044</v>
+      </c>
+      <c r="K12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>700</v>
+      </c>
+      <c r="B13">
+        <v>0.01</v>
+      </c>
+      <c r="C13">
+        <v>0.1</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
+      </c>
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>0.05</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0.044</v>
+      </c>
+      <c r="K13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>800</v>
+      </c>
+      <c r="B14">
+        <v>0.01</v>
+      </c>
+      <c r="C14">
+        <v>0.1</v>
+      </c>
+      <c r="D14">
+        <v>1000</v>
+      </c>
+      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0.05</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0.047</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>900</v>
+      </c>
+      <c r="B15">
+        <v>0.01</v>
+      </c>
+      <c r="C15">
+        <v>0.1</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
+      </c>
+      <c r="E15">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>0.05</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0.046</v>
+      </c>
+      <c r="K15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>1000</v>
+      </c>
+      <c r="B16">
+        <v>0.01</v>
+      </c>
+      <c r="C16">
+        <v>0.1</v>
+      </c>
+      <c r="D16">
+        <v>1000</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>0.05</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0.034</v>
+      </c>
+      <c r="K16">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
